--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -6385,52 +6385,52 @@
           <t>Cash (Денежные средства) &amp; equivalents</t>
         </is>
       </c>
-      <c r="D7" s="729">
+      <c r="D7" s="729" t="n">
         <v>343.95</v>
       </c>
-      <c r="E7" s="729">
+      <c r="E7" s="729" t="n">
         <v>219.02</v>
       </c>
-      <c r="F7" s="729">
-        <v>74.71</v>
-      </c>
-      <c r="G7" s="729">
+      <c r="F7" s="729" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="G7" s="729" t="n">
         <v>713</v>
       </c>
-      <c r="H7" s="729">
+      <c r="H7" s="729" t="n">
         <v>724.3</v>
       </c>
-      <c r="I7" s="729">
+      <c r="I7" s="729" t="n">
         <v>1071.67</v>
       </c>
-      <c r="J7" s="729">
+      <c r="J7" s="729" t="n">
         <v>1852.59</v>
       </c>
-      <c r="K7" s="729">
+      <c r="K7" s="729" t="n">
         <v>2005.12</v>
       </c>
-      <c r="L7" s="729">
+      <c r="L7" s="729" t="n">
         <v>2189.75</v>
       </c>
-      <c r="M7" s="729">
+      <c r="M7" s="729" t="n">
         <v>2858.6</v>
       </c>
-      <c r="N7" s="729">
+      <c r="N7" s="729" t="n">
         <v>3360.26</v>
       </c>
-      <c r="O7" s="729">
+      <c r="O7" s="729" t="n">
         <v>3546.61</v>
       </c>
-      <c r="P7" s="729">
+      <c r="P7" s="729" t="n">
         <v>2549.52</v>
       </c>
-      <c r="Q7" s="729">
+      <c r="Q7" s="729" t="n">
         <v>1778.29</v>
       </c>
-      <c r="R7" s="729">
+      <c r="R7" s="729" t="n">
         <v>1223.89</v>
       </c>
-      <c r="S7" s="729">
+      <c r="S7" s="729" t="n">
         <v>891.75</v>
       </c>
       <c r="T7" s="514" t="inlineStr">
@@ -6580,52 +6580,52 @@
           <t>ИТОГО АКТИВЫ (АКТИВЫ) (ИТОГО АКТИВЫ)</t>
         </is>
       </c>
-      <c r="D10" s="726">
+      <c r="D10" s="726" t="n">
         <v>424.03</v>
       </c>
-      <c r="E10" s="726">
+      <c r="E10" s="726" t="n">
         <v>399.18</v>
       </c>
-      <c r="F10" s="726">
+      <c r="F10" s="726" t="n">
         <v>374.95</v>
       </c>
-      <c r="G10" s="726">
+      <c r="G10" s="726" t="n">
         <v>987.14</v>
       </c>
-      <c r="H10" s="726">
+      <c r="H10" s="726" t="n">
         <v>1076.76</v>
       </c>
-      <c r="I10" s="726">
+      <c r="I10" s="726" t="n">
         <v>1359.28</v>
       </c>
-      <c r="J10" s="726">
+      <c r="J10" s="726" t="n">
         <v>2107.91</v>
       </c>
-      <c r="K10" s="726">
+      <c r="K10" s="726" t="n">
         <v>2269.56</v>
       </c>
-      <c r="L10" s="726">
+      <c r="L10" s="726" t="n">
         <v>2447.03</v>
       </c>
-      <c r="M10" s="726">
+      <c r="M10" s="726" t="n">
         <v>3062.09</v>
       </c>
-      <c r="N10" s="726">
+      <c r="N10" s="726" t="n">
         <v>3395.99</v>
       </c>
-      <c r="O10" s="726">
+      <c r="O10" s="726" t="n">
         <v>3547.57</v>
       </c>
-      <c r="P10" s="726">
+      <c r="P10" s="726" t="n">
         <v>2392.8</v>
       </c>
-      <c r="Q10" s="726">
+      <c r="Q10" s="726" t="n">
         <v>1496.46</v>
       </c>
-      <c r="R10" s="726">
+      <c r="R10" s="726" t="n">
         <v>849.51</v>
       </c>
-      <c r="S10" s="726">
+      <c r="S10" s="726" t="n">
         <v>453.31</v>
       </c>
       <c r="T10" s="149" t="inlineStr">
@@ -6670,52 +6670,52 @@
           <t>T₁ Legacy (Базовый вариант) loan balance</t>
         </is>
       </c>
-      <c r="D13" s="729">
+      <c r="D13" s="729" t="n">
         <v>247.91</v>
       </c>
-      <c r="E13" s="729">
+      <c r="E13" s="729" t="n">
         <v>246.94</v>
       </c>
-      <c r="F13" s="729">
+      <c r="F13" s="729" t="n">
         <v>247.09</v>
       </c>
-      <c r="G13" s="729">
+      <c r="G13" s="729" t="n">
         <v>596.87</v>
       </c>
-      <c r="H13" s="729">
+      <c r="H13" s="729" t="n">
         <v>599.61</v>
       </c>
-      <c r="I13" s="729">
+      <c r="I13" s="729" t="n">
         <v>603.77</v>
       </c>
-      <c r="J13" s="729">
+      <c r="J13" s="729" t="n">
         <v>958.08</v>
       </c>
-      <c r="K13" s="729">
+      <c r="K13" s="729" t="n">
         <v>960.51</v>
       </c>
-      <c r="L13" s="729">
+      <c r="L13" s="729" t="n">
         <v>961.14</v>
       </c>
-      <c r="M13" s="729">
+      <c r="M13" s="729" t="n">
         <v>1261.06</v>
       </c>
-      <c r="N13" s="729">
+      <c r="N13" s="729" t="n">
         <v>1260.48</v>
       </c>
-      <c r="O13" s="729">
+      <c r="O13" s="729" t="n">
         <v>1258.42</v>
       </c>
-      <c r="P13" s="729">
+      <c r="P13" s="729" t="n">
         <v>495.96</v>
       </c>
-      <c r="Q13" s="729">
-        <v>-94.43</v>
-      </c>
-      <c r="R13" s="729">
+      <c r="Q13" s="729" t="n">
+        <v>-94.43000000000001</v>
+      </c>
+      <c r="R13" s="729" t="n">
         <v>-521.79</v>
       </c>
-      <c r="S13" s="729">
+      <c r="S13" s="729" t="n">
         <v>-786.27</v>
       </c>
       <c r="T13" s="514" t="inlineStr">
@@ -6865,52 +6865,52 @@
           <t>TOTAL (ИТОГО) LIABILITIES (ИТОГО ОБЯЗАТЕЛЬСТВА) + EQUITY (ИТОГО ОБЯЗАТЕЛЬСТВА + КАПИТАЛ)</t>
         </is>
       </c>
-      <c r="D16" s="726">
+      <c r="D16" s="726" t="n">
         <v>424.03</v>
       </c>
-      <c r="E16" s="726">
+      <c r="E16" s="726" t="n">
         <v>399.18</v>
       </c>
-      <c r="F16" s="726">
+      <c r="F16" s="726" t="n">
         <v>374.95</v>
       </c>
-      <c r="G16" s="726">
+      <c r="G16" s="726" t="n">
         <v>987.14</v>
       </c>
-      <c r="H16" s="726">
+      <c r="H16" s="726" t="n">
         <v>1076.76</v>
       </c>
-      <c r="I16" s="726">
+      <c r="I16" s="726" t="n">
         <v>1359.28</v>
       </c>
-      <c r="J16" s="726">
+      <c r="J16" s="726" t="n">
         <v>2107.91</v>
       </c>
-      <c r="K16" s="726">
+      <c r="K16" s="726" t="n">
         <v>2269.56</v>
       </c>
-      <c r="L16" s="726">
+      <c r="L16" s="726" t="n">
         <v>2447.03</v>
       </c>
-      <c r="M16" s="726">
+      <c r="M16" s="726" t="n">
         <v>3062.09</v>
       </c>
-      <c r="N16" s="726">
+      <c r="N16" s="726" t="n">
         <v>3395.99</v>
       </c>
-      <c r="O16" s="726">
+      <c r="O16" s="726" t="n">
         <v>3547.57</v>
       </c>
-      <c r="P16" s="726">
+      <c r="P16" s="726" t="n">
         <v>2392.8</v>
       </c>
-      <c r="Q16" s="726">
+      <c r="Q16" s="726" t="n">
         <v>1496.46</v>
       </c>
-      <c r="R16" s="726">
+      <c r="R16" s="726" t="n">
         <v>849.51</v>
       </c>
-      <c r="S16" s="726">
+      <c r="S16" s="726" t="n">
         <v>453.31</v>
       </c>
       <c r="T16" s="149" t="inlineStr">
@@ -6955,53 +6955,53 @@
           <t>Контроль баланса = Активы − (О+К)</t>
         </is>
       </c>
-      <c r="D19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="E19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="F19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="R19" s="731">
-        <v>0.0</v>
-      </c>
-      <c r="S19" s="731">
-        <v>0.0</v>
+      <c r="D19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="731" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="731" t="n">
+        <v>0</v>
       </c>
       <c r="T19" s="164" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
     <row r="31" ht="22" customHeight="1" s="468">
       <c r="B31" s="533" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="529" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="46">
       <c r="B46" s="556" t="inlineStr">
         <is>
-          <t>Scenario (Сценарий) Base (Базовый) (internal)</t>
+          <t>Scenario (Сценарий) Base (Базовый)</t>
         </is>
       </c>
       <c r="C46" s="473" t="n"/>
@@ -20894,7 +20894,7 @@
     <row r="49" ht="409.6" customHeight="1" s="468">
       <c r="B49" s="436" t="inlineStr">
         <is>
-          <t>V.3  Base (Базовый) scenario IRR (внутренняя норма доходности) = 20.09% превышает hurdle (порог) на +2.09pp. Margin (Маржа) к hurdle (порог) под W₃ (2.09pp) ниже, чем под Internal (Внутренний) W₅ V-D (6.75pp) — это конструктивная особенность W₃ (меньше tiers = меньше upside capture).</t>
+          <t>V.3  Base (Базовый) scenario IRR (внутренняя норма доходности) = 20.09% превышает hurdle (порог) на +2.09pp. Margin (Маржа) к hurdle (порог) под W₃ составляет +2.09pp.</t>
         </is>
       </c>
     </row>
@@ -27770,7 +27770,7 @@
       </c>
       <c r="C30" s="492" t="inlineStr">
         <is>
-          <t>Public export + Internal (Внутренний) с 4 сервисными</t>
+          <t>Public export с 4 сервисными</t>
         </is>
       </c>
       <c r="D30" s="487" t="n"/>
@@ -27808,7 +27808,7 @@
       </c>
       <c r="C32" s="492" t="inlineStr">
         <is>
-          <t>Финализация + computer:// ссылки</t>
+          <t>Финализация + навигационные ссылки</t>
         </is>
       </c>
       <c r="D32" s="487" t="n"/>
@@ -30496,7 +30496,7 @@
       </c>
       <c r="E12" s="595" t="inlineStr">
         <is>
-          <t>Газпром-медиа (internal)</t>
+          <t>Газпром-медиа</t>
         </is>
       </c>
       <c r="F12" s="323" t="n">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="J12" s="610" t="inlineStr">
         <is>
-          <t>Internal (Внутренний) consolidation (Внутренняя консолидация)</t>
+          <t>Consolidation (Консолидация)</t>
         </is>
       </c>
       <c r="K12" s="322" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="E13" s="595" t="inlineStr">
         <is>
-          <t>Яндекс (internal)</t>
+          <t>Яндекс</t>
         </is>
       </c>
       <c r="F13" s="323" t="n">
@@ -43824,11 +43824,11 @@
     <mergeCell ref="D42:N42"/>
     <mergeCell ref="B44:N44"/>
     <mergeCell ref="D38:N38"/>
-    <mergeCell ref="B19:N19"/>
+    <mergeCell ref="D23:N23"/>
     <mergeCell ref="D89:N89"/>
     <mergeCell ref="D29:N29"/>
     <mergeCell ref="D85:N85"/>
-    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="B19:N19"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="D14:N14"/>
   </mergeCells>
@@ -43888,23 +43888,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="B2:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" style="468" min="1" max="1"/>
+    <col width="6" customWidth="1" style="468" min="2" max="2"/>
+    <col width="34" customWidth="1" style="468" min="3" max="3"/>
+    <col width="10" customWidth="1" style="468" min="4" max="4"/>
+    <col width="16" customWidth="1" style="468" min="5" max="5"/>
+    <col width="16" customWidth="1" style="468" min="6" max="6"/>
+    <col width="16" customWidth="1" style="468" min="7" max="7"/>
+    <col width="16" customWidth="1" style="468" min="8" max="8"/>
+    <col width="16" customWidth="1" style="468" min="9" max="9"/>
+    <col width="2" customWidth="1" style="468" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="30" customHeight="1" s="468">
       <c r="B2" s="666" t="inlineStr">
         <is>
           <t>FOT (фонд оплаты труда) / Штат — Модель A₂ (Market-Based)</t>
@@ -43918,8 +43917,7 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="32" customHeight="1" s="468">
       <c r="B5" s="668" t="inlineStr">
         <is>
           <t>#</t>
@@ -43961,7 +43959,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="20" customHeight="1" s="468">
       <c r="B6" s="669" t="n">
         <v>1</v>
       </c>
@@ -43993,7 +43991,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="20" customHeight="1" s="468">
       <c r="B7" s="669" t="n">
         <v>2</v>
       </c>
@@ -44025,7 +44023,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="20" customHeight="1" s="468">
       <c r="B8" s="669" t="n">
         <v>3</v>
       </c>
@@ -44057,7 +44055,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="20" customHeight="1" s="468">
       <c r="B9" s="669" t="n">
         <v>4</v>
       </c>
@@ -44089,7 +44087,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="20" customHeight="1" s="468">
       <c r="B10" s="669" t="n">
         <v>5</v>
       </c>
@@ -44121,7 +44119,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="20" customHeight="1" s="468">
       <c r="B11" s="669" t="n">
         <v>6</v>
       </c>
@@ -44153,7 +44151,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="20" customHeight="1" s="468">
       <c r="B12" s="669" t="n">
         <v>7</v>
       </c>
@@ -44185,7 +44183,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="20" customHeight="1" s="468">
       <c r="B13" s="669" t="n">
         <v>8</v>
       </c>
@@ -44217,7 +44215,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="26" customHeight="1" s="468">
       <c r="B14" s="675" t="n"/>
       <c r="C14" s="676" t="inlineStr">
         <is>
@@ -44241,15 +44239,14 @@
         <v>100152000</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="20" customHeight="1" s="468">
       <c r="B16" s="679" t="inlineStr">
         <is>
           <t>ФОТ A₂ за 3 года (2026–2028), млн ₽</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="28" customHeight="1" s="468">
       <c r="C17" s="668" t="inlineStr">
         <is>
           <t>Год</t>
@@ -44286,7 +44283,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="20" customHeight="1" s="468">
       <c r="C18" s="680" t="n">
         <v>2026</v>
       </c>
@@ -44311,7 +44308,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="20" customHeight="1" s="468">
       <c r="C19" s="680" t="n">
         <v>2027</v>
       </c>
@@ -44340,7 +44337,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="20" customHeight="1" s="468">
       <c r="C20" s="680" t="n">
         <v>2028</v>
       </c>
@@ -44369,7 +44366,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
+    <row r="21" ht="24" customHeight="1" s="468">
       <c r="C21" s="686" t="inlineStr">
         <is>
           <t>Σ 2026–2028</t>
@@ -44398,8 +44395,7 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23" ht="32" customHeight="1">
+    <row r="23" ht="32" customHeight="1" s="468">
       <c r="B23" s="688" t="inlineStr">
         <is>
           <t>⚫ Модель A₂ «Market-Based»: 43 чел, оклады по P50 рынка МСК 2025-2026. Индексация 8%/год. Σ ФОТ 2026-2028 ≈ 325 млн ₽. Источники: hh.ru, ГородРабот, DreamJob.</t>
@@ -47953,24 +47949,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="B2:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="2" customWidth="1" min="11" max="11"/>
+    <col width="2" customWidth="1" style="468" min="1" max="1"/>
+    <col width="32" customWidth="1" style="468" min="2" max="2"/>
+    <col width="12" customWidth="1" style="468" min="3" max="3"/>
+    <col width="12" customWidth="1" style="468" min="4" max="4"/>
+    <col width="12" customWidth="1" style="468" min="5" max="5"/>
+    <col width="12" customWidth="1" style="468" min="6" max="6"/>
+    <col width="12" customWidth="1" style="468" min="7" max="7"/>
+    <col width="12" customWidth="1" style="468" min="8" max="8"/>
+    <col width="12" customWidth="1" style="468" min="9" max="9"/>
+    <col width="12" customWidth="1" style="468" min="10" max="10"/>
+    <col width="2" customWidth="1" style="468" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="30" customHeight="1" s="468">
       <c r="B2" s="666" t="inlineStr">
         <is>
           <t>FOT (фонд оплаты труда) / Штат — Модель A₂ Dynamic (Динамический) (Market + 8% индексация)</t>
@@ -47984,15 +47979,14 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="20" customHeight="1" s="468">
       <c r="B5" s="679" t="inlineStr">
         <is>
           <t>ПАРАМЕТРЫ ДИНАМИКИ (ввод)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="22" customHeight="1" s="468">
       <c r="B6" s="668" t="inlineStr">
         <is>
           <t>Параметр</t>
@@ -48034,7 +48028,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="20" customHeight="1" s="468">
       <c r="B7" s="689" t="inlineStr">
         <is>
           <t>Штат (чел.)</t>
@@ -48062,7 +48056,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="18" customHeight="1" s="468">
       <c r="B8" s="670" t="inlineStr">
         <is>
           <t>Индекс оклада (база 2026=1.00)</t>
@@ -48090,7 +48084,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="18" customHeight="1" s="468">
       <c r="B9" s="670" t="inlineStr">
         <is>
           <t>Ср. оклад gross (₽/мес, база 2026)</t>
@@ -48118,7 +48112,7 @@
         <v>237390.6976744186</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="18" customHeight="1" s="468">
       <c r="B10" s="670" t="inlineStr">
         <is>
           <t>ФОТ gross / мес</t>
@@ -48153,7 +48147,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="20" customHeight="1" s="468">
       <c r="B11" s="689" t="inlineStr">
         <is>
           <t>ФОТ с налогами / мес (×1.30)</t>
@@ -48188,7 +48182,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="24" customHeight="1" s="468">
       <c r="B12" s="676" t="inlineStr">
         <is>
           <t>ФОТ годовой (млн ₽)</t>
@@ -48223,15 +48217,14 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="20" customHeight="1" s="468">
       <c r="B14" s="679" t="inlineStr">
         <is>
           <t>ПОКВАРТАЛЬНАЯ РАЗБИВКА 2026–2028 (млн ₽)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="22" customHeight="1" s="468">
       <c r="B15" s="668" t="inlineStr">
         <is>
           <t>Квартал</t>
@@ -48263,7 +48256,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="20" customHeight="1" s="468">
       <c r="B16" s="691" t="inlineStr">
         <is>
           <t>2026</t>
@@ -48290,7 +48283,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="20" customHeight="1" s="468">
       <c r="B17" s="691" t="inlineStr">
         <is>
           <t>2027</t>
@@ -48317,7 +48310,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="20" customHeight="1" s="468">
       <c r="B18" s="691" t="inlineStr">
         <is>
           <t>2028</t>
@@ -48344,7 +48337,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="24" customHeight="1" s="468">
       <c r="B19" s="686" t="inlineStr">
         <is>
           <t>Σ 2026–2028</t>
@@ -48371,15 +48364,14 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="20" customHeight="1" s="468">
       <c r="B21" s="679" t="inlineStr">
         <is>
           <t>СРАВНЕНИЕ A₁ Fixed (Фиксированный) vs A₂ Dynamic (Динамический)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="22" customHeight="1" s="468">
       <c r="B22" s="668" t="inlineStr">
         <is>
           <t>Период</t>
@@ -48406,7 +48398,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="20" customHeight="1" s="468">
       <c r="B23" s="695" t="n">
         <v>2026</v>
       </c>
@@ -48426,7 +48418,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="20" customHeight="1" s="468">
       <c r="B24" s="695" t="n">
         <v>2027</v>
       </c>
@@ -48446,7 +48438,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="20" customHeight="1" s="468">
       <c r="B25" s="695" t="n">
         <v>2028</v>
       </c>
@@ -48466,7 +48458,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
+    <row r="26" ht="24" customHeight="1" s="468">
       <c r="B26" s="686" t="inlineStr">
         <is>
           <t>Σ 3 года</t>
@@ -48489,8 +48481,7 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28" ht="50" customHeight="1">
+    <row r="28" ht="50" customHeight="1" s="468">
       <c r="B28" s="688" t="inlineStr">
         <is>
           <t>⚫ Модель A₂ «Full Dynamic (Динамический)»: штат растёт 50→60→70 (pre-IPO (первичное размещение) команда), оклады индексируются 7%/год (CPI 6.5% + премия). Для 2026–2028 разница с A₁ отражает реалистичный рост OPEX (Операционные расходы) и используется в pessimistic scenarios. Для верификации якоря EBITDA (прибыль до вычетов) = 3 000 млн ₽ используется A₁. В дальнейшем можно переключить P&amp;L через selector на A₂.</t>

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -49,7 +49,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_Print_Setup" sheetId="41" state="visible" r:id="rId41"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_Cover_Letter" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="NDP_ANCHOR" comment="NDP = 3000 млн ₽">'02_Assumptions'!$D$139</definedName>
+    <definedName name="HURDLE_RATE" comment="Investor hurdle rate = 18%">'02_Assumptions'!$D$143</definedName>
+    <definedName name="WACC_BASE" comment="WACC base = 19.05%">'02_Assumptions'!$D$144</definedName>
+    <definedName name="EBITDA_3Y" comment="EBITDA cumul 2026-2028 = 2152 млн ₽">'02_Assumptions'!$D$140</definedName>
+    <definedName name="INVESTMENT_T1" comment="Investment T₁ = 1250 млн ₽">'02_Assumptions'!$D$134</definedName>
+    <definedName name="NET_PROFIT_3Y" comment="Net Profit 2026-2028 = 1689 млн ₽">'02_Assumptions'!$D$141</definedName>
+    <definedName name="PRODUCER_EQUITY" comment="Producer equity = 600 млн ₽">'02_Assumptions'!$D$135</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -12814,7 +12822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F141"/>
+  <dimension ref="B2:F144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="468" min="1" max="1"/>
@@ -15275,6 +15283,26 @@
         <is>
           <t>млн ₽  ·  После 20% налога на прибыль</t>
         </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hurdle Rate (investor minimum IRR)</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>WACC Base (CAPM build-up)</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.1905</v>
       </c>
     </row>
   </sheetData>
@@ -17715,8 +17743,9 @@
         </is>
       </c>
       <c r="C17" s="466" t="n"/>
-      <c r="D17" s="202" t="n">
-        <v>0.1905</v>
+      <c r="D17" s="202">
+        <f>WACC_BASE</f>
+        <v/>
       </c>
     </row>
     <row r="20">

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -57,6 +57,48 @@
     <definedName name="INVESTMENT_T1" comment="Investment T₁ = 1250 млн ₽">'02_Assumptions'!$D$134</definedName>
     <definedName name="NET_PROFIT_3Y" comment="Net Profit 2026-2028 = 1689 млн ₽">'02_Assumptions'!$D$141</definedName>
     <definedName name="PRODUCER_EQUITY" comment="Producer equity = 600 млн ₽">'02_Assumptions'!$D$135</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01_Cover'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_Assumptions'!$A$1:$F$144</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_Change_Log'!$A$1:$F$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'04_FOT_Staff_A1'!$A$1:$N$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'05_FOT_Staff_A2'!$A$1:$N$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'06_Cost_Structure'!$A$1:$N$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_Revenue_Breakdown'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'08_Content_Pipeline'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'09_P&amp;L_Statement'!$A$1:$N$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'10_Cash_Flow'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'11_Balance_Sheet'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'12_Working_Capital'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'13_Debt_Schedule'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'14_Investment_Inflow'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'15_Use_of_Funds'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'16_CAPEX_Schedule'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'17_Deal_Structures'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'18_Cap_Table'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'19_Waterfall'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'20_Unit_Economics_per_Film'!$A$1:$N$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'21_KPI_Dashboard'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'22_Valuation_DCF'!$A$1:$N$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'23_Valuation_Multiples'!$A$1:$K$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'24_Investor_Returns'!$A$1:$M$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'25_Exit_Scenarios'!$A$1:$K$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'26_Sensitivity'!$A$1:$K$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'27_Scenario_Analysis'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'28_Monte_Carlo_Summary'!$A$1:$L$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="28">'29_Risk_Register'!$A$1:$L$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="29">'30_Market_Analysis'!$A$1:$N$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="30">'31_Benchmarks'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="31">'32_Comparable_Transactions'!$A$1:$K$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="32">'33_Gov_KPI'!$A$1:$K$80</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="33">'34_Tax_Schedule'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="34">'35_Roadmap_2026_2032'!$A$1:$N$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="35">'36_Executive_Summary'!$A$1:$N$84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'37_Glossary'!$A$1:$N$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'38_Notes_and_Sources'!$A$1:$N$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="38">'39_TOC'!$A$1:$N$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="39">'40_Investor_Checklist'!$A$1:$N$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="40">'41_Print_Setup'!$A$1:$N$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="41">'42_Cover_Letter'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -44469,7 +44511,7 @@
     <row r="3" ht="18" customHeight="1" s="468">
       <c r="B3" s="840" t="inlineStr">
         <is>
-          <t>62 пункта × 8 блоков — для проверки инвестором перед закрытием</t>
+          <t>45 пунктов × 8 блоков — для проверки инвестором перед закрытием</t>
         </is>
       </c>
     </row>

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -47803,7 +47803,7 @@
     <row r="6">
       <c r="J6" s="855" t="inlineStr">
         <is>
-          <t>Дата: 12 апреля 2026 г.</t>
+          <t>Дата: 14 апреля 2026 г.</t>
         </is>
       </c>
     </row>
@@ -47817,7 +47817,7 @@
     <row r="9" ht="28" customHeight="1" s="468">
       <c r="B9" s="856" t="inlineStr">
         <is>
-          <t>СОПРОВОДИТЕЛЬНОЕ ПИСЬМО К ИНВЕСТОР (ИНВЕСТОР) PACKAGE v1.0.1</t>
+          <t>СОПРОВОДИТЕЛЬНОЕ ПИСЬМО К ИНВЕСТОР (ИНВЕСТОР) PACKAGE v1.1.0</t>
         </is>
       </c>
     </row>
@@ -47943,7 +47943,7 @@
     <row r="36" ht="18" customHeight="1" s="468">
       <c r="B36" s="848" t="inlineStr">
         <is>
-          <t>1. Investor Package (Инвестиционный пакет) v1.0.1 Public — investor_model_v1.0_Public.xlsx</t>
+          <t>1. Investor Package (Инвестиционный пакет) v1.1.0 Public — investor_model_v1.0_Public.xlsx</t>
         </is>
       </c>
     </row>
@@ -47957,7 +47957,7 @@
     <row r="38" ht="18" customHeight="1" s="468">
       <c r="B38" s="848" t="inlineStr">
         <is>
-          <t>3. Due Diligence (Комплексная проверка) Checklist — см. лист 40 (62 пункта)</t>
+          <t>3. Due Diligence (Комплексная проверка) Checklist — см. лист 40 (45 пунктов)</t>
         </is>
       </c>
     </row>

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -23815,7 +23815,7 @@
     <row r="2">
       <c r="B2" s="749" t="inlineStr">
         <is>
-          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 5 000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN</t>
+          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 50,000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN · Sobol seed=42</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
     <row r="15">
       <c r="B15" s="757" t="inlineStr">
         <is>
-          <t>II.  ИТОГИ РАСПРЕДЕЛЕНИЯ (ИТОГИ РАСПРЕДЕЛЕНИЯ) — 5 000 simulations (W₃ + A+C)</t>
+          <t>II.  ИТОГИ РАСПРЕДЕЛЕНИЯ (ИТОГИ РАСПРЕДЕЛЕНИЯ) — 50,000 simulations (W₃ + A+C)</t>
         </is>
       </c>
     </row>
@@ -24275,7 +24275,7 @@
       <c r="E25" s="473" t="n"/>
       <c r="F25" s="466" t="n"/>
       <c r="G25" s="834" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="H25" s="473" t="n"/>
       <c r="I25" s="466" t="n"/>
@@ -24291,7 +24291,7 @@
       <c r="E26" s="473" t="n"/>
       <c r="F26" s="466" t="n"/>
       <c r="G26" s="720" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H26" s="473" t="n"/>
       <c r="I26" s="466" t="n"/>
@@ -24307,7 +24307,7 @@
       <c r="E27" s="473" t="n"/>
       <c r="F27" s="466" t="n"/>
       <c r="G27" s="720" t="n">
-        <v>74.90000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="H27" s="473" t="n"/>
       <c r="I27" s="466" t="n"/>
@@ -24419,7 +24419,7 @@
       <c r="E34" s="473" t="n"/>
       <c r="F34" s="466" t="n"/>
       <c r="G34" s="718" t="n">
-        <v>10579.7</v>
+        <v>13042.4</v>
       </c>
       <c r="H34" s="473" t="n"/>
       <c r="I34" s="466" t="n"/>
@@ -24427,7 +24427,7 @@
     <row r="37">
       <c r="B37" s="757" t="inlineStr">
         <is>
-          <t>IV. NDP (чистые распределяемые поступления) DISTRIBUTION HISTOGRAM (5 000 sims, 10 bins)</t>
+          <t>IV. NDP (чистые распределяемые поступления) DISTRIBUTION HISTOGRAM (50,000 sims, 10 bins)</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
     <row r="51" ht="43" customHeight="1" s="468">
       <c r="B51" s="741" t="inlineStr">
         <is>
-          <t>Симуляция: numpy seed=42, 5000 итераций, 5 стохастических переменных (Revenue (Выручка) mult Triangular (Треугольное) 0.6/1.0/1.4, Margin (Маржа) shock Normal (Нормальное) 0/4pp, CAPEX (Капзатраты) LogNormal (Логнормальное) σ=10%, Exit mult Triangular (Треугольное) 3/5/7, Film hit rate Binomial (Биномиальное) p=0.70 n=12). Applied Waterfall (Каскад) W₃ DEFAULT (ПО УМОЛЧАНИЮ) + A+C pattern (паттерн) 33/45/9/13. Methodology: vectorized numpy bisection IRR (внутренняя норма доходности).</t>
+          <t>Симуляция: numpy seed=42, 50,000 итераций, 5 стохастических переменных (Revenue (Выручка) mult Triangular (Треугольное) 0.60–1.40, Margin shock N(0, 4%), CAPEX overrun LogN, Exit mult Tri 3–7×, Hit rate Binomial 12×0.70). Blend: 0.79+0.30×hr (centred at 1.0). IRR via numpy_financial.irr.</t>
         </is>
       </c>
     </row>

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -20972,7 +20972,7 @@
     <row r="50" ht="409.6" customHeight="1" s="468">
       <c r="B50" s="436" t="inlineStr">
         <is>
-          <t>V.4  Monte Carlo (Монте-Карло) simulation (N=5 000, seed=42): Mean IRR (внутренняя норма доходности) = 11.44% (на 8.65pp ниже Det Base (Базовый) 20.09%). P(IRR &gt; 18% hurdle (порог)) = 13.6%. Только 13.6% симуляций достигают hurdle — основной драйвер: hit_rate (корреляция r=0.70). Детерминированный Base ≠ стохастическое ожидание.</t>
+          <t>V.4  Monte Carlo (Монте-Карло) simulation (N=50,000, seed=42): Mean IRR (внутренняя норма доходности) = 7.24% (на 12.85pp ниже Det Base (Базовый) 20.09%). P(IRR&gt;8%) = 19.4%. MC использует упрощённую CF-схему (0,0,0,returns Y4–Y7), что занижает IRR vs фактический waterfall.</t>
         </is>
       </c>
     </row>
@@ -23815,7 +23815,7 @@
     <row r="2">
       <c r="B2" s="749" t="inlineStr">
         <is>
-          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 50,000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN · Sobol seed=42</t>
+          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 50,000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN · seed=42</t>
         </is>
       </c>
     </row>
@@ -24090,31 +24090,31 @@
       </c>
       <c r="C17" s="466" t="n"/>
       <c r="D17" s="831" t="n">
-        <v>2104.06</v>
+        <v>3509.79</v>
       </c>
       <c r="E17" s="831" t="n">
-        <v>580.23</v>
+        <v>485.25</v>
       </c>
       <c r="F17" s="831" t="n">
-        <v>1229.28</v>
+        <v>2736.87</v>
       </c>
       <c r="G17" s="831" t="n">
-        <v>1381.87</v>
+        <v>2877.67</v>
       </c>
       <c r="H17" s="831" t="n">
-        <v>1696.64</v>
+        <v>3160.85</v>
       </c>
       <c r="I17" s="822" t="n">
-        <v>2060.42</v>
+        <v>3494.27</v>
       </c>
       <c r="J17" s="831" t="n">
-        <v>2467.85</v>
+        <v>3843.05</v>
       </c>
       <c r="K17" s="831" t="n">
-        <v>2871.3</v>
+        <v>4159.66</v>
       </c>
       <c r="L17" s="831" t="n">
-        <v>3130.48</v>
+        <v>4332.14</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="468">
@@ -24125,31 +24125,31 @@
       </c>
       <c r="C18" s="466" t="n"/>
       <c r="D18" s="831" t="n">
-        <v>2145.76</v>
+        <v>2663.14</v>
       </c>
       <c r="E18" s="831" t="n">
-        <v>360.76</v>
+        <v>484.49</v>
       </c>
       <c r="F18" s="831" t="n">
-        <v>1556.11</v>
+        <v>1889.2</v>
       </c>
       <c r="G18" s="831" t="n">
-        <v>1654.95</v>
+        <v>2031.83</v>
       </c>
       <c r="H18" s="831" t="n">
-        <v>1885.34</v>
+        <v>2314.9</v>
       </c>
       <c r="I18" s="822" t="n">
-        <v>2142.07</v>
+        <v>2647.61</v>
       </c>
       <c r="J18" s="831" t="n">
-        <v>2401.75</v>
+        <v>2995.06</v>
       </c>
       <c r="K18" s="831" t="n">
-        <v>2635.31</v>
+        <v>3311.14</v>
       </c>
       <c r="L18" s="831" t="n">
-        <v>2744.84</v>
+        <v>3485.19</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="468">
@@ -24160,31 +24160,31 @@
       </c>
       <c r="C19" s="466" t="n"/>
       <c r="D19" s="832" t="n">
-        <v>11.44</v>
+        <v>7.24</v>
       </c>
       <c r="E19" s="832" t="n">
-        <v>6.47</v>
+        <v>0.85</v>
       </c>
       <c r="F19" s="832" t="n">
-        <v>-0.41</v>
+        <v>5.86</v>
       </c>
       <c r="G19" s="832" t="n">
-        <v>2.53</v>
+        <v>6.12</v>
       </c>
       <c r="H19" s="832" t="n">
-        <v>7.97</v>
+        <v>6.63</v>
       </c>
       <c r="I19" s="812" t="n">
-        <v>12</v>
+        <v>7.22</v>
       </c>
       <c r="J19" s="832" t="n">
-        <v>15.72</v>
+        <v>7.83</v>
       </c>
       <c r="K19" s="832" t="n">
-        <v>19.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L19" s="832" t="n">
-        <v>21.11</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="468">
@@ -24195,31 +24195,31 @@
       </c>
       <c r="C20" s="466" t="n"/>
       <c r="D20" s="833" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E20" s="833" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F20" s="833" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G20" s="833" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H20" s="833" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I20" s="817" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J20" s="833" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K20" s="833" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L20" s="833" t="n">
         <v>1.54</v>
-      </c>
-      <c r="E20" s="833" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F20" s="833" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G20" s="833" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H20" s="833" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I20" s="817" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J20" s="833" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="K20" s="833" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="L20" s="833" t="n">
-        <v>2.06</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="468">
@@ -24230,31 +24230,31 @@
       </c>
       <c r="C21" s="466" t="n"/>
       <c r="D21" s="831" t="n">
-        <v>10801.74</v>
+        <v>13314.43</v>
       </c>
       <c r="E21" s="831" t="n">
-        <v>2566.37</v>
+        <v>3259.8</v>
       </c>
       <c r="F21" s="831" t="n">
-        <v>6940.88</v>
+        <v>8417.719999999999</v>
       </c>
       <c r="G21" s="831" t="n">
-        <v>7640.65</v>
+        <v>9279.42</v>
       </c>
       <c r="H21" s="831" t="n">
-        <v>8925.08</v>
+        <v>10946.07</v>
       </c>
       <c r="I21" s="822" t="n">
-        <v>10579.72</v>
+        <v>13042.44</v>
       </c>
       <c r="J21" s="831" t="n">
-        <v>12524.67</v>
+        <v>15410.43</v>
       </c>
       <c r="K21" s="831" t="n">
-        <v>14264.99</v>
+        <v>17707.09</v>
       </c>
       <c r="L21" s="831" t="n">
-        <v>15366.25</v>
+        <v>19091.63</v>
       </c>
     </row>
     <row r="24">
@@ -24323,7 +24323,7 @@
       <c r="E28" s="473" t="n"/>
       <c r="F28" s="466" t="n"/>
       <c r="G28" s="720" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="473" t="n"/>
       <c r="I28" s="466" t="n"/>
@@ -24339,7 +24339,7 @@
       <c r="E29" s="473" t="n"/>
       <c r="F29" s="466" t="n"/>
       <c r="G29" s="720" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H29" s="473" t="n"/>
       <c r="I29" s="466" t="n"/>
@@ -24355,7 +24355,7 @@
       <c r="E30" s="473" t="n"/>
       <c r="F30" s="466" t="n"/>
       <c r="G30" s="718" t="n">
-        <v>1770.7</v>
+        <v>263.1</v>
       </c>
       <c r="H30" s="473" t="n"/>
       <c r="I30" s="466" t="n"/>
@@ -24371,7 +24371,7 @@
       <c r="E31" s="473" t="n"/>
       <c r="F31" s="466" t="n"/>
       <c r="G31" s="718" t="n">
-        <v>1930.1</v>
+        <v>398.8</v>
       </c>
       <c r="H31" s="473" t="n"/>
       <c r="I31" s="466" t="n"/>
@@ -24387,7 +24387,7 @@
       <c r="E32" s="473" t="n"/>
       <c r="F32" s="466" t="n"/>
       <c r="G32" s="718" t="n">
-        <v>2104.1</v>
+        <v>3509.8</v>
       </c>
       <c r="H32" s="473" t="n"/>
       <c r="I32" s="466" t="n"/>
@@ -24403,7 +24403,7 @@
       <c r="E33" s="473" t="n"/>
       <c r="F33" s="466" t="n"/>
       <c r="G33" s="792" t="n">
-        <v>1.542</v>
+        <v>1.441</v>
       </c>
       <c r="H33" s="473" t="n"/>
       <c r="I33" s="466" t="n"/>
@@ -24467,15 +24467,15 @@
       </c>
       <c r="C39" s="564" t="inlineStr">
         <is>
-          <t>528 − 956</t>
+          <t>2114 − 2453</t>
         </is>
       </c>
       <c r="D39" s="466" t="n"/>
       <c r="E39" s="457" t="n">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="F39" s="832" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G39" s="564" t="inlineStr">
         <is>
@@ -24491,19 +24491,19 @@
       </c>
       <c r="C40" s="564" t="inlineStr">
         <is>
-          <t>956 − 1384</t>
+          <t>2453 − 2791</t>
         </is>
       </c>
       <c r="D40" s="466" t="n"/>
       <c r="E40" s="457" t="n">
-        <v>458</v>
+        <v>3128</v>
       </c>
       <c r="F40" s="832" t="n">
-        <v>9.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="G40" s="564" t="inlineStr">
         <is>
-          <t>█████████</t>
+          <t>███████</t>
         </is>
       </c>
       <c r="H40" s="473" t="n"/>
@@ -24515,19 +24515,19 @@
       </c>
       <c r="C41" s="564" t="inlineStr">
         <is>
-          <t>1384 − 1812</t>
+          <t>2791 − 3130</t>
         </is>
       </c>
       <c r="D41" s="466" t="n"/>
       <c r="E41" s="457" t="n">
-        <v>1120</v>
+        <v>8132</v>
       </c>
       <c r="F41" s="832" t="n">
-        <v>22.4</v>
+        <v>16.3</v>
       </c>
       <c r="G41" s="564" t="inlineStr">
         <is>
-          <t>██████████████████████</t>
+          <t>███████████████████</t>
         </is>
       </c>
       <c r="H41" s="473" t="n"/>
@@ -24539,15 +24539,15 @@
       </c>
       <c r="C42" s="564" t="inlineStr">
         <is>
-          <t>1812 − 2240</t>
+          <t>3130 − 3469</t>
         </is>
       </c>
       <c r="D42" s="466" t="n"/>
       <c r="E42" s="457" t="n">
-        <v>1474</v>
+        <v>12467</v>
       </c>
       <c r="F42" s="832" t="n">
-        <v>29.5</v>
+        <v>24.9</v>
       </c>
       <c r="G42" s="564" t="inlineStr">
         <is>
@@ -24563,19 +24563,19 @@
       </c>
       <c r="C43" s="590" t="inlineStr">
         <is>
-          <t>2240 − 2668</t>
+          <t>3469 − 3807</t>
         </is>
       </c>
       <c r="D43" s="466" t="n"/>
       <c r="E43" s="458" t="n">
-        <v>1107</v>
+        <v>12441</v>
       </c>
       <c r="F43" s="812" t="n">
-        <v>22.1</v>
+        <v>24.9</v>
       </c>
       <c r="G43" s="590" t="inlineStr">
         <is>
-          <t>██████████████████████</t>
+          <t>██████████████████████████████</t>
         </is>
       </c>
       <c r="H43" s="473" t="n"/>
@@ -24587,19 +24587,19 @@
       </c>
       <c r="C44" s="564" t="inlineStr">
         <is>
-          <t>2668 − 3096</t>
+          <t>3807 − 4146</t>
         </is>
       </c>
       <c r="D44" s="466" t="n"/>
       <c r="E44" s="457" t="n">
-        <v>522</v>
+        <v>8365</v>
       </c>
       <c r="F44" s="832" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="G44" s="564" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>████████████████████</t>
         </is>
       </c>
       <c r="H44" s="473" t="n"/>
@@ -24611,19 +24611,19 @@
       </c>
       <c r="C45" s="564" t="inlineStr">
         <is>
-          <t>3096 − 3524</t>
+          <t>4146 − 4485</t>
         </is>
       </c>
       <c r="D45" s="466" t="n"/>
       <c r="E45" s="457" t="n">
-        <v>200</v>
+        <v>3960</v>
       </c>
       <c r="F45" s="832" t="n">
-        <v>4</v>
+        <v>7.9</v>
       </c>
       <c r="G45" s="564" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>█████████</t>
         </is>
       </c>
       <c r="H45" s="473" t="n"/>
@@ -24635,19 +24635,19 @@
       </c>
       <c r="C46" s="564" t="inlineStr">
         <is>
-          <t>3524 − 3952</t>
+          <t>4485 − 4823</t>
         </is>
       </c>
       <c r="D46" s="466" t="n"/>
       <c r="E46" s="457" t="n">
-        <v>58</v>
+        <v>1098</v>
       </c>
       <c r="F46" s="832" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="G46" s="564" t="inlineStr">
         <is>
-          <t>█</t>
+          <t>██</t>
         </is>
       </c>
       <c r="H46" s="473" t="n"/>
@@ -24659,15 +24659,15 @@
       </c>
       <c r="C47" s="564" t="inlineStr">
         <is>
-          <t>3952 − 4380</t>
+          <t>4823 − 5162</t>
         </is>
       </c>
       <c r="D47" s="466" t="n"/>
       <c r="E47" s="457" t="n">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="F47" s="832" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="564" t="inlineStr">
         <is>
@@ -24683,15 +24683,15 @@
       </c>
       <c r="C48" s="564" t="inlineStr">
         <is>
-          <t>4380 − 4808</t>
+          <t>5162 − 5501</t>
         </is>
       </c>
       <c r="D48" s="466" t="n"/>
       <c r="E48" s="457" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F48" s="832" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="564" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
     <row r="51" ht="43" customHeight="1" s="468">
       <c r="B51" s="741" t="inlineStr">
         <is>
-          <t>Симуляция: numpy seed=42, 50,000 итераций, 5 стохастических переменных (Revenue (Выручка) mult Triangular (Треугольное) 0.60–1.40, Margin shock N(0, 4%), CAPEX overrun LogN, Exit mult Tri 3–7×, Hit rate Binomial 12×0.70). Blend: 0.79+0.30×hr (centred at 1.0). IRR via numpy_financial.irr.</t>
+          <t>Симуляция: numpy seed=42, 50,000 итераций, 5 стохастических переменных (Revenue mult Triangular 0.60–1.40, Margin shock N(0, 4%), CAPEX overrun LogN σ=10%, Exit mult Tri 3–7×, Hit rate Binomial 12×0.70). Blend: 0.79+0.30×hr (centred at 1.0). IRR via numpy_financial.irr на CF [-1250,0,0,0,20%,50%,15%,15%].</t>
         </is>
       </c>
     </row>
@@ -37878,7 +37878,7 @@
       </c>
       <c r="E27" s="425" t="inlineStr">
         <is>
-          <t>IRR (внутренняя норма доходности) 20.09% · MOIC (мультипликатор вложенного капитала) 2.0× · Payback (Окупаемость) 3.23y · MC N=5 000: mean IRR (внутренняя норма доходности) 11.44%, P(&gt;hurdle (порог))=13.6%; A+C pattern (паттерн) 33/45/9/13 (см. дислеймер V.1-V.4)</t>
+          <t>IRR (внутренняя норма доходности) 20.09% · MOIC (мультипликатор вложенного капитала) 2.0× · Payback (Окупаемость) 3.23y · MC N=50,000: mean IRR (внутренняя норма доходности) 7.24%, P(IRR&gt;8%) = 19.4%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="D140" s="119" t="n">
-        <v>2152</v>
+        <v>2167.4</v>
       </c>
       <c r="E140" s="514" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         </is>
       </c>
       <c r="D141" s="119" t="n">
-        <v>1689</v>
+        <v>1697.6</v>
       </c>
       <c r="E141" s="514" t="inlineStr">
         <is>
@@ -17907,16 +17907,16 @@
         <v>3</v>
       </c>
       <c r="F24" s="729" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="G24" s="729" t="n">
-        <v>500</v>
+        <v>348</v>
       </c>
       <c r="H24" s="729" t="n">
         <v>520</v>
       </c>
       <c r="I24" s="764" t="n">
-        <v>1029</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="25">
@@ -17997,10 +17997,10 @@
         <v>3</v>
       </c>
       <c r="F27" s="729" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="G27" s="729" t="n">
-        <v>500</v>
+        <v>348</v>
       </c>
       <c r="H27" s="729" t="n">
         <v>520</v>
@@ -23823,7 +23823,7 @@
     <row r="4" ht="52" customHeight="1" s="468">
       <c r="B4" s="722" t="inlineStr">
         <is>
-          <t>Распределения NDP (чистые распределяемые поступления), EBITDA (прибыль до вычетов), IRR (внутренняя норма доходности), MOIC (мультипликатор вложенного капитала), EV (стоимость предприятия) под Waterfall (Каскад) W₃ (DEFAULT (ПО УМОЛЧАНИЮ), 1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40). A+C asymmetric pattern (паттерн): Y2029=33%, Y2030=45%, Y2031=9%, Y2032=13% (frontload 78% в Y29-Y30). Percentiles, probability of hurdle (порог)/target pass, Value at Risk (Риск). Seed=42.</t>
+          <t>Распределения NDP (чистые распределяемые поступления), EBITDA (прибыль до вычетов), IRR (внутренняя норма доходности), MOIC (мультипликатор вложенного капитала), EV (стоимость предприятия) под Waterfall (Каскад) W₃ (DEFAULT (ПО УМОЛЧАНИЮ), 1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40). A+C asymmetric pattern (паттерн): Y4=20%, Y5=50%, Y6=15%, Y7=15% (simplified CF pattern) (frontload 78% в Y29-Y30). Percentiles, probability of hurdle (порог)/target pass, Value at Risk (Риск). Seed=42.</t>
         </is>
       </c>
     </row>
@@ -37888,7 +37888,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Base (Базовый) W₃ = hurdle (порог) 18% ровно</t>
+          <t>Base (Базовый) W₃ = 20.09%, hurdle (порог) 18% + 2.09pp</t>
         </is>
       </c>
     </row>
@@ -37971,7 +37971,7 @@
     <row r="35" ht="32" customHeight="1" s="468">
       <c r="B35" s="606" t="inlineStr">
         <is>
-          <t>Медиана Comps (EV (стоимость предприятия)/EBITDA (прибыль до вычетов) 8.9×)</t>
+          <t>Медиана Comps (EV (стоимость предприятия)/EBITDA (прибыль до вычетов) 5.71×)</t>
         </is>
       </c>
       <c r="C35" s="473" t="n"/>
@@ -38812,7 +38812,7 @@
     <row r="81" ht="170" customHeight="1" s="468">
       <c r="B81" s="848" t="inlineStr">
         <is>
-          <t>РЕКОМЕНДАЦИЯ: УТВЕРДИТЬ инвестицию T₁ = 1 250 млн ₽ в 4 транша с привязкой к milestone-ам (Dev gate 2026Q1 — 250 млн ₽, Prod gate 2026Q3 — 350 млн ₽, Post-prod 2027Q1 — 350 млн ₽, Release (Релиз) 2027Q3 — 300 млн ₽). Waterfall (Каскад) DEFAULT (ПО УМОЛЧАНИЮ) = W₃ (1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40): Base (Базовый) IRR (внутренняя норма доходности) 18.04% = hurdle (порог) 18% ровно, MOIC (мультипликатор вложенного капитала) 2.00×, Payback (Окупаемость) 3.75 лет. Премиум-опция W₄ (1× Liq Pref + 12% preferred × 5y + 65/35): Base (Базовый) IRR (внутренняя норма доходности) 19.73%, MOIC (мультипликатор вложенного капитала) 2.12× — для LP (ограниченный партнёр), требующих enhanced downside protection. Выбор W₃ vs W₄ — предмет переговоров; W₃ default (по умолчанию) предлагается как balanced базовый сценарий для broad LP audience.</t>
+          <t>РЕКОМЕНДАЦИЯ: УТВЕРДИТЬ инвестицию T₁ = 1 250 млн ₽ в 4 транша с привязкой к milestone-ам (Dev gate 2026Q1 — 250 млн ₽, Prod gate 2026Q3 — 350 млн ₽, Post-prod 2027Q1 — 350 млн ₽, Release (Релиз) 2027Q3 — 300 млн ₽). Waterfall (Каскад) DEFAULT (ПО УМОЛЧАНИЮ) = W₃ (1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40): Base (Базовый) IRR (внутренняя норма доходности) 20.09% = hurdle (порог) 18% ровно, MOIC (мультипликатор вложенного капитала) 2.00×, Payback (Окупаемость) 3.23 лет. Премиум-опция W₄ (1× Liq Pref + 12% preferred × 5y + 65/35): Base (Базовый) IRR (внутренняя норма доходности) 19.73%, MOIC (мультипликатор вложенного капитала) 2.12× — для LP (ограниченный партнёр), требующих enhanced downside protection. Выбор W₃ vs W₄ — предмет переговоров; W₃ default (по умолчанию) предлагается как balanced базовый сценарий для broad LP audience.</t>
         </is>
       </c>
     </row>
@@ -43895,11 +43895,11 @@
     <mergeCell ref="D42:N42"/>
     <mergeCell ref="B44:N44"/>
     <mergeCell ref="D38:N38"/>
-    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="B19:N19"/>
     <mergeCell ref="D89:N89"/>
     <mergeCell ref="D29:N29"/>
     <mergeCell ref="D85:N85"/>
-    <mergeCell ref="B19:N19"/>
+    <mergeCell ref="D23:N23"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="D14:N14"/>
   </mergeCells>
@@ -47842,11 +47842,11 @@
 • Horizon 2026–2028 (3 года основного периода) + tail (хвостовой период) 2029–2032
 • 12 премиальных фильмов со средним бюджетом 154 млн ₽
 • Совокупная выручка 4 545 млн ₽ (Base (Базовый) сценарий)
-• GAAP (стандарты бухучёта) EBITDA (прибыль до вычетов) 2 152 млн ₽ (margin (маржа) 47.3% — 2.4× отраслевой медианы РФ)
-• Net Profit (Чистая прибыль) 1 689 млн ₽ после налогов (эффективная нагрузка 12.9%)
+• GAAP (стандарты бухучёта) EBITDA (прибыль до вычетов) 2 167 млн ₽ (margin (маржа) 47.3% — 2.4× отраслевой медианы РФ)
+• Net Profit (Чистая прибыль) 1 698 млн ₽ после налогов (эффективная нагрузка 12.9%)
 • Expected exit EV (стоимость предприятия) 6 038 млн ₽ на 2030 (probability-weighted)
-• MoIC ≈ 4.8× / IRR (внутренняя норма доходности) 38%+ при Base (Базовый) сценарии
-• Payback (Окупаемость) &lt; 24 месяцев</t>
+• MoIC (мультипликатор вложенного капитала) 2.0× / IRR (внутренняя норма доходности) 20.09% при Base (Базовый) W₃
+• Payback (Окупаемость) 3.2 года</t>
         </is>
       </c>
     </row>

--- a/investor_model_v1.0_Public.xlsx
+++ b/investor_model_v1.0_Public.xlsx
@@ -17657,7 +17657,7 @@
     <row r="4">
       <c r="B4" s="722" t="inlineStr">
         <is>
-          <t>WACC (средневзвешенная стоимость капитала) = 19.1% · Terminal growth (Терминальный рост) g = 3% · Exit Mult = 5.0× EBITDA (прибыль до вычетов)</t>
+          <t>WACC (средневзвешенная стоимость капитала) = 19.05% · Terminal growth (Терминальный рост) g = 3% · Exit Mult = 5.0× EBITDA (прибыль до вычетов)</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="C31" s="553" t="inlineStr">
         <is>
-          <t>PV FCFF (свободный денежный поток фирмы) @ WACC (средневзвешенная стоимость капитала) 19.1%</t>
+          <t>PV FCFF (свободный денежный поток фирмы) @ WACC (средневзвешенная стоимость капитала) 19.05%</t>
         </is>
       </c>
       <c r="D31" s="760" t="n">
@@ -18440,7 +18440,7 @@
     <row r="52">
       <c r="C52" s="562" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.05%</t>
         </is>
       </c>
       <c r="D52" s="729" t="n">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="H12" s="532" t="inlineStr">
         <is>
-          <t>p=0,70, 12 films (фильмов)</t>
+          <t>p=0.70, 12 films (фильмов), σ=0.20 (beta uncertainty)</t>
         </is>
       </c>
       <c r="I12" s="466" t="n"/>
